--- a/Practicas/cronograma excel.xlsx
+++ b/Practicas/cronograma excel.xlsx
@@ -1,19 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Documents\gitPrimer-Semestre-25\Practicas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B318C641-19C4-4F4F-9F46-6D99B1C841CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2424DDEE-F7C3-4652-921E-C418558F01A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{693F3BED-ABCA-4C35-84F7-5735A91B3CFA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{693F3BED-ABCA-4C35-84F7-5735A91B3CFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1 (2)" sheetId="3" r:id="rId2"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId3"/>
+    <sheet name="Hoja4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
   <si>
     <t>Actividades</t>
   </si>
@@ -100,13 +103,214 @@
   </si>
   <si>
     <t>No.</t>
+  </si>
+  <si>
+    <t>Introducción al curso y diagnóstico</t>
+  </si>
+  <si>
+    <t>Unidad 1: Ecuaciones y desigualdades</t>
+  </si>
+  <si>
+    <t>Unidad 2: Geometría</t>
+  </si>
+  <si>
+    <t>Unidad 3: Gráficas y funciones</t>
+  </si>
+  <si>
+    <t>Unidad 4: Funciones polinomiales y racionales</t>
+  </si>
+  <si>
+    <t>Unidad 5: Funciones exponenciales y logarítmicas</t>
+  </si>
+  <si>
+    <t>Semana</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Unidad / Tema</t>
+  </si>
+  <si>
+    <t>Actividades del Laboratorio</t>
+  </si>
+  <si>
+    <t>Producto / Evaluación</t>
+  </si>
+  <si>
+    <t>Ponderación</t>
+  </si>
+  <si>
+    <t>11-15 agosto</t>
+  </si>
+  <si>
+    <t>Prueba diagnóstica, hoja de repaso, dinámicas grupales</t>
+  </si>
+  <si>
+    <t>Lista de cotejo</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>18-29 agosto</t>
+  </si>
+  <si>
+    <t>Resolución de ecuaciones, uso de números complejos, modelado</t>
+  </si>
+  <si>
+    <t>Hoja de trabajo</t>
+  </si>
+  <si>
+    <t>1-12 septiembre</t>
+  </si>
+  <si>
+    <t>Construcción de modelos geométricos, cálculo de áreas y volúmenes</t>
+  </si>
+  <si>
+    <t>Modelos + ejercicios</t>
+  </si>
+  <si>
+    <t>15-19 septiembre</t>
+  </si>
+  <si>
+    <t>Graficación con software, funciones lineales, transformaciones</t>
+  </si>
+  <si>
+    <t>Hoja + lectura</t>
+  </si>
+  <si>
+    <t>22 sept - 3 octubre</t>
+  </si>
+  <si>
+    <t>División de polinomios, ceros, modelos aplicados</t>
+  </si>
+  <si>
+    <t>Ejercicios + modelo</t>
+  </si>
+  <si>
+    <t>6-10 octubre</t>
+  </si>
+  <si>
+    <t>Leyes de logaritmos, modelado de crecimiento o decaimiento</t>
+  </si>
+  <si>
+    <t>13-17 octubre</t>
+  </si>
+  <si>
+    <t>Proyecto intermedio</t>
+  </si>
+  <si>
+    <t>Desarrollo de un caso aplicado con funciones</t>
+  </si>
+  <si>
+    <t>Informe + presentación</t>
+  </si>
+  <si>
+    <t>20-31 octubre</t>
+  </si>
+  <si>
+    <t>Unidad 6: Trigonometría</t>
+  </si>
+  <si>
+    <t>Gráficas trigonométricas, ley de senos y cosenos</t>
+  </si>
+  <si>
+    <t>Hoja + discusión</t>
+  </si>
+  <si>
+    <t>3-7 noviembre</t>
+  </si>
+  <si>
+    <t>Unidad 7: Geometría Analítica</t>
+  </si>
+  <si>
+    <t>Parábola, elipse, hipérbola con graficación y análisis</t>
+  </si>
+  <si>
+    <t>10-14 noviembre</t>
+  </si>
+  <si>
+    <t>Presentación de proyecto final</t>
+  </si>
+  <si>
+    <t>Proyecto integrador con aplicación real</t>
+  </si>
+  <si>
+    <t>Exposición + entrega escrita</t>
+  </si>
+  <si>
+    <t>Total acumulado en todo el curso</t>
+  </si>
+  <si>
+    <t>100% (20 pts)</t>
+  </si>
+  <si>
+    <t>Claro, aquí tienes el texto en tercera persona y en forma concisa:</t>
+  </si>
+  <si>
+    <t>El curso inicia con una prueba diagnóstica, hoja de repaso y dinámicas grupales, evaluadas mediante una lista de cotejo.</t>
+  </si>
+  <si>
+    <t>Se trabaja la resolución de ecuaciones y desigualdades, el uso de números complejos y el modelado, con una hoja de trabajo como evidencia.</t>
+  </si>
+  <si>
+    <t>Se desarrolla la construcción de modelos geométricos y el cálculo de áreas y volúmenes, evaluados con ejercicios y modelos elaborados por los estudiantes.</t>
+  </si>
+  <si>
+    <t>Se aplica software para graficar funciones lineales y sus transformaciones, con hoja de trabajo y lectura como evidencias.</t>
+  </si>
+  <si>
+    <t>Se estudia la división de polinomios, la identificación de ceros y la aplicación de modelos, evaluados mediante ejercicios y un modelo contextual.</t>
+  </si>
+  <si>
+    <t>Se modelan fenómenos de crecimiento y decaimiento con funciones exponenciales y logarítmicas, utilizando una hoja de trabajo.</t>
+  </si>
+  <si>
+    <t>El proyecto intermedio consiste en la resolución de un caso aplicado con funciones, con entrega de informe y presentación oral.</t>
+  </si>
+  <si>
+    <t>Se abordan gráficas trigonométricas y leyes de senos y cosenos, con hoja de trabajo y discusión grupal.</t>
+  </si>
+  <si>
+    <t>Se analizan y grafican la parábola, la elipse y la hipérbola, con una hoja de trabajo como evidencia.</t>
+  </si>
+  <si>
+    <t>El proyecto final integra todos los contenidos del curso en una aplicación real, evaluado mediante exposición oral y entrega escrita.</t>
+  </si>
+  <si>
+    <t>Prueba diagnóstica, hoja de repaso y dinámicas grupales, evaluadas mediante una lista de cotejo.</t>
+  </si>
+  <si>
+    <t>Resolución de ecuaciones y desigualdades, el uso de números complejos y el modelado, con una hoja de trabajo como evidencia.</t>
+  </si>
+  <si>
+    <t>Resolución de  modelos geométricos y el cálculo de áreas y volúmenes, evaluados con ejercicios y modelos elaborados por los estudiantes.</t>
+  </si>
+  <si>
+    <t>Aplicar software para graficar funciones lineales y sus transformaciones, con hoja de trabajo y lectura como evidencias.</t>
+  </si>
+  <si>
+    <t>Modelado de fenómenos de crecimiento y decaimiento con funciones exponenciales y logarítmicas, utilizando una hoja de trabajo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolución de un caso aplicado con funciones, con entrega de informe </t>
+  </si>
+  <si>
+    <t>Realización de gráficas trigonométricas y leyes de senos y cosenos, con hoja de trabajo y discusión grupal.</t>
+  </si>
+  <si>
+    <t>Integrar todos los contenidos del curso en una aplicación real, Con hoja de trabajo</t>
+  </si>
+  <si>
+    <t>Duración Estimada de Docencia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,8 +334,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -162,6 +389,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -310,7 +543,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -318,9 +551,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
@@ -342,42 +572,88 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -705,84 +981,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="16"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="26"/>
     </row>
     <row r="2" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="13"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="17" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17" t="s">
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="18" t="s">
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="4" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="19" t="s">
+    <row r="3" spans="1:11" s="3" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="31"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="19" t="s">
+      <c r="J3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="20" t="s">
+      <c r="K3" s="12" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21">
+      <c r="A4" s="13">
         <v>1</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -791,16 +1067,16 @@
       <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21">
+      <c r="A5" s="13">
         <v>2</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -808,95 +1084,95 @@
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21">
+      <c r="A6" s="13">
         <v>3</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21">
+      <c r="A7" s="13">
         <v>4</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="2"/>
     </row>
     <row r="8" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21">
+      <c r="A8" s="13">
         <v>5</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
       <c r="J8" s="1"/>
       <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21">
+      <c r="A9" s="13">
         <v>6</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="6"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="5"/>
     </row>
     <row r="10" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21">
+      <c r="A10" s="13">
         <v>7</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
       <c r="K10" s="2"/>
     </row>
     <row r="11" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21">
+      <c r="A11" s="13">
         <v>8</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="1"/>
@@ -904,44 +1180,44 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="6"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="5"/>
     </row>
     <row r="12" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21">
+      <c r="A12" s="13">
         <v>9</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
       <c r="K12" s="2"/>
     </row>
     <row r="13" spans="1:11" ht="93.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22">
+      <c r="A13" s="14">
         <v>10</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="8"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -953,4 +1229,627 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E75DA7F1-605D-4134-8590-05421821D0AF}">
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="46" style="37" customWidth="1"/>
+    <col min="3" max="14" width="7.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="26"/>
+    </row>
+    <row r="2" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="31"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="32"/>
+    </row>
+    <row r="3" spans="1:14" s="3" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="20">
+        <v>1</v>
+      </c>
+      <c r="D3" s="20">
+        <v>2</v>
+      </c>
+      <c r="E3" s="20">
+        <v>3</v>
+      </c>
+      <c r="F3" s="20">
+        <v>4</v>
+      </c>
+      <c r="G3" s="20">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20">
+        <v>2</v>
+      </c>
+      <c r="I3" s="20">
+        <v>3</v>
+      </c>
+      <c r="J3" s="20">
+        <v>4</v>
+      </c>
+      <c r="K3" s="20">
+        <v>1</v>
+      </c>
+      <c r="L3" s="20">
+        <v>2</v>
+      </c>
+      <c r="M3" s="20">
+        <v>3</v>
+      </c>
+      <c r="N3" s="23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13">
+        <v>1</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="2"/>
+    </row>
+    <row r="5" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13">
+        <v>2</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="2"/>
+    </row>
+    <row r="6" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13">
+        <v>3</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="2"/>
+    </row>
+    <row r="7" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13">
+        <v>4</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13">
+        <v>5</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="2"/>
+    </row>
+    <row r="9" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13">
+        <v>6</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="2"/>
+    </row>
+    <row r="10" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13">
+        <v>7</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="2"/>
+    </row>
+    <row r="11" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13">
+        <v>8</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="2"/>
+    </row>
+    <row r="12" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13">
+        <v>9</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="2"/>
+    </row>
+    <row r="13" spans="1:14" ht="105" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="14">
+        <v>10</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="C1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E23571D-7CFE-4DA0-8AF2-E5574AAB884F}">
+  <dimension ref="D5:I16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="5" spans="4:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="D5" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="4:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="D6" s="15">
+        <v>1</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="4:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="D7" s="17">
+        <v>45718</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="19">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8" spans="4:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="D8" s="17">
+        <v>45781</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="19">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="9" spans="4:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="D9" s="15">
+        <v>6</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="19">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10" spans="4:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="D10" s="17">
+        <v>45876</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="19">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="11" spans="4:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="D11" s="15">
+        <v>9</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" s="19">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12" spans="4:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="D12" s="15">
+        <v>10</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" s="19">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="13" spans="4:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="D13" s="17">
+        <v>46002</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="I13" s="19">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14" spans="4:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="D14" s="15">
+        <v>13</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I14" s="19">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="15" spans="4:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="D15" s="15">
+        <v>14</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" s="19">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16" spans="4:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="D16" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D483543-C16C-42CF-BC43-DD1A48771E7B}">
+  <dimension ref="E7:E17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="7" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Practicas/cronograma excel.xlsx
+++ b/Practicas/cronograma excel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Documents\gitPrimer-Semestre-25\Practicas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitPrimer-Semetre-25\Practicas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2424DDEE-F7C3-4652-921E-C418558F01A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9FB2F7-5381-4E6A-A230-DD1D110E6CE1}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{693F3BED-ABCA-4C35-84F7-5735A91B3CFA}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Hoja2" sheetId="2" r:id="rId3"/>
     <sheet name="Hoja4" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="93">
   <si>
     <t>Actividades</t>
   </si>
@@ -304,6 +304,9 @@
   </si>
   <si>
     <t>Duración Estimada de Docencia</t>
+  </si>
+  <si>
+    <t>Resolución de polinomios, la identificación de ceros y la aplicación de modelos, evaluados mediante ejercicios y un modelo contextual.</t>
   </si>
 </sst>
 </file>
@@ -617,6 +620,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -638,22 +648,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -974,53 +977,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11FB33A-2EC9-4470-A975-E750206C5AD9}">
   <dimension ref="A1:K13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
-    <col min="3" max="11" width="10.140625" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" customWidth="1"/>
+    <col min="3" max="11" width="10.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="26"/>
-    </row>
-    <row r="2" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="27" t="s">
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="29"/>
+    </row>
+    <row r="2" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="34"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27" t="s">
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
       <c r="K2" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="3" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="31"/>
-      <c r="B3" s="29"/>
+    <row r="3" spans="1:11" s="3" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="34"/>
+      <c r="B3" s="32"/>
       <c r="C3" s="11" t="s">
         <v>1</v>
       </c>
@@ -1049,7 +1052,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="13">
         <v>1</v>
       </c>
@@ -1066,7 +1069,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="13">
         <v>2</v>
       </c>
@@ -1083,7 +1086,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="13">
         <v>3</v>
       </c>
@@ -1100,7 +1103,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="13">
         <v>4</v>
       </c>
@@ -1117,7 +1120,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="13">
         <v>5</v>
       </c>
@@ -1134,7 +1137,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="13">
         <v>6</v>
       </c>
@@ -1151,7 +1154,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="13">
         <v>7</v>
       </c>
@@ -1168,7 +1171,7 @@
       <c r="J10" s="4"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="13">
         <v>8</v>
       </c>
@@ -1185,7 +1188,7 @@
       <c r="J11" s="4"/>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="13">
         <v>9</v>
       </c>
@@ -1202,7 +1205,7 @@
       <c r="J12" s="4"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" ht="93.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="93.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14">
         <v>10</v>
       </c>
@@ -1233,126 +1236,106 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E75DA7F1-605D-4134-8590-05421821D0AF}">
-  <dimension ref="A1:N13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:O14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" customWidth="1"/>
-    <col min="2" max="2" width="46" style="37" customWidth="1"/>
-    <col min="3" max="14" width="7.140625" customWidth="1"/>
+    <col min="2" max="2" width="8.453125" customWidth="1"/>
+    <col min="3" max="3" width="46" style="27" customWidth="1"/>
+    <col min="4" max="15" width="7.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="2:15" ht="20" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="2" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B2" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="C2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="D2" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="26"/>
-    </row>
-    <row r="2" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="27" t="s">
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="29"/>
+    </row>
+    <row r="3" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B3" s="34"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27" t="s">
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27" t="s">
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="32"/>
-    </row>
-    <row r="3" spans="1:14" s="3" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="31"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="20">
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="37"/>
+    </row>
+    <row r="4" spans="2:15" s="3" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="34"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="20">
         <v>1</v>
       </c>
-      <c r="D3" s="20">
+      <c r="E4" s="20">
         <v>2</v>
       </c>
-      <c r="E3" s="20">
+      <c r="F4" s="20">
         <v>3</v>
       </c>
-      <c r="F3" s="20">
+      <c r="G4" s="20">
         <v>4</v>
       </c>
-      <c r="G3" s="20">
+      <c r="H4" s="20">
         <v>1</v>
       </c>
-      <c r="H3" s="20">
+      <c r="I4" s="20">
         <v>2</v>
       </c>
-      <c r="I3" s="20">
+      <c r="J4" s="20">
         <v>3</v>
       </c>
-      <c r="J3" s="20">
+      <c r="K4" s="20">
         <v>4</v>
       </c>
-      <c r="K3" s="20">
+      <c r="L4" s="20">
         <v>1</v>
       </c>
-      <c r="L3" s="20">
+      <c r="M4" s="20">
         <v>2</v>
       </c>
-      <c r="M3" s="20">
+      <c r="N4" s="20">
         <v>3</v>
       </c>
-      <c r="N3" s="23">
+      <c r="O4" s="23">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+    <row r="5" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="13">
         <v>1</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="C5" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="2"/>
-    </row>
-    <row r="5" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13">
-        <v>2</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="1"/>
       <c r="D5" s="22"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1363,19 +1346,19 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="2"/>
-    </row>
-    <row r="6" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13">
-        <v>3</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="13">
+        <v>2</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>84</v>
+      </c>
       <c r="D6" s="1"/>
       <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
+      <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -1383,19 +1366,19 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-    </row>
-    <row r="7" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13">
-        <v>4</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="2"/>
+    </row>
+    <row r="7" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="13">
+        <v>3</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>85</v>
+      </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+      <c r="F7" s="22"/>
       <c r="G7" s="22"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -1403,56 +1386,56 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13">
-        <v>5</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="13">
+        <v>4</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>86</v>
+      </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
+      <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
-      <c r="N8" s="2"/>
-    </row>
-    <row r="9" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13">
-        <v>6</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="13">
+        <v>5</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>92</v>
+      </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+      <c r="I9" s="22"/>
       <c r="J9" s="22"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
-      <c r="N9" s="2"/>
-    </row>
-    <row r="10" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13">
-        <v>7</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="13">
+        <v>6</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>87</v>
+      </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -1463,16 +1446,16 @@
       <c r="K10" s="22"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
-      <c r="N10" s="2"/>
-    </row>
-    <row r="11" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13">
-        <v>8</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="13">
+        <v>7</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>88</v>
+      </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -1483,16 +1466,16 @@
       <c r="K11" s="1"/>
       <c r="L11" s="22"/>
       <c r="M11" s="1"/>
-      <c r="N11" s="2"/>
-    </row>
-    <row r="12" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13">
-        <v>9</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="2"/>
+    </row>
+    <row r="12" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="13">
+        <v>8</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>89</v>
+      </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -1503,36 +1486,57 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="22"/>
-      <c r="N12" s="2"/>
-    </row>
-    <row r="13" spans="1:14" ht="105" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14">
+      <c r="N12" s="1"/>
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="13">
+        <v>9</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" spans="2:15" ht="105" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="14">
         <v>10</v>
       </c>
-      <c r="B13" s="36" t="s">
+      <c r="C14" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="24"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="C1:N1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="D2:O2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1542,9 +1546,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E23571D-7CFE-4DA0-8AF2-E5574AAB884F}">
   <dimension ref="D5:I16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="5" spans="4:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="D5" s="16" t="s">
         <v>31</v>
       </c>
@@ -1564,7 +1568,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="4:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:9" ht="87" x14ac:dyDescent="0.35">
       <c r="D6" s="15">
         <v>1</v>
       </c>
@@ -1584,7 +1588,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="4:9" ht="105" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:9" ht="101.5" x14ac:dyDescent="0.35">
       <c r="D7" s="17">
         <v>45718</v>
       </c>
@@ -1604,7 +1608,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="4:9" ht="105" x14ac:dyDescent="0.25">
+    <row r="8" spans="4:9" ht="101.5" x14ac:dyDescent="0.35">
       <c r="D8" s="17">
         <v>45781</v>
       </c>
@@ -1624,7 +1628,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="9" spans="4:9" ht="105" x14ac:dyDescent="0.25">
+    <row r="9" spans="4:9" ht="101.5" x14ac:dyDescent="0.35">
       <c r="D9" s="15">
         <v>6</v>
       </c>
@@ -1644,7 +1648,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="10" spans="4:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="D10" s="17">
         <v>45876</v>
       </c>
@@ -1664,7 +1668,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="11" spans="4:9" ht="120" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:9" ht="116" x14ac:dyDescent="0.35">
       <c r="D11" s="15">
         <v>9</v>
       </c>
@@ -1684,7 +1688,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="4:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="12" spans="4:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="D12" s="15">
         <v>10</v>
       </c>
@@ -1704,7 +1708,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="13" spans="4:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="13" spans="4:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="D13" s="17">
         <v>46002</v>
       </c>
@@ -1724,7 +1728,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="14" spans="4:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:9" ht="87" x14ac:dyDescent="0.35">
       <c r="D14" s="15">
         <v>13</v>
       </c>
@@ -1744,7 +1748,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="15" spans="4:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="15" spans="4:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="D15" s="15">
         <v>14</v>
       </c>
@@ -1764,7 +1768,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="16" spans="4:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="4:9" ht="58" x14ac:dyDescent="0.35">
       <c r="D16" s="15" t="s">
         <v>40</v>
       </c>
@@ -1792,59 +1796,59 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D483543-C16C-42CF-BC43-DD1A48771E7B}">
   <dimension ref="E7:E17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="7" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E7" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E8" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E9" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E11" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E12" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E14" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E15" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E16" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E17" t="s">
         <v>82</v>
       </c>
